--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21391,7 +21409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21462,6 +21480,115 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1973_74_0064 'TJ Spartak Lada Soběslav' ROZBITÝ prev CLUB_S1972_73_0117 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1973_74_0086 'TJ Žďas Žďár nad Sázavou' prev→CLUB_S1972_73_0455 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0013</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1973_74_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0025</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0025 'KVAL  skupina A' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0026 'KVAL  skupina B' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0027</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0027 'KVAL přímé postupy JM/SM' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0028</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0028 'KVAL skupina D (jen raw/prepared)' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -35060,7 +35187,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -35125,7 +35251,6 @@
         </is>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -55788,6 +55913,215 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0064</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0064 'TJ Spartak Lada Soběslav' ROZBITÝ prev CLUB_S1972_73_0117 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0086</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0086 'TJ Žďas Žďár nad Sázavou' prev→CLUB_S1972_73_0455 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0013</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1973_74_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1973_74_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0025</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1973_74_0025 'KVAL  skupina A' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0026</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1973_74_0026 'KVAL  skupina B' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0027</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1973_74_0027 'KVAL přímé postupy JM/SM' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0028</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1973_74_0028 'KVAL skupina D (jen raw/prepared)' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5532,11 +5532,7 @@
           <t>CLUB_S1973_74_0369</t>
         </is>
       </c>
-      <c r="R64" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
+      <c r="R64" s="3" t="n"/>
       <c r="S64" s="3" t="n"/>
       <c r="T64" s="3" t="n"/>
       <c r="U64" s="3" t="n"/>
@@ -5675,11 +5671,7 @@
           <t>CLUB_S1973_74_0372</t>
         </is>
       </c>
-      <c r="R67" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
+      <c r="R67" s="3" t="n"/>
       <c r="S67" s="3" t="n"/>
       <c r="T67" s="3" t="n"/>
       <c r="U67" s="3" t="n"/>
@@ -5773,11 +5765,7 @@
           <t>CLUB_S1973_74_0374</t>
         </is>
       </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
+      <c r="R69" s="3" t="n"/>
       <c r="S69" s="3" t="n"/>
       <c r="T69" s="3" t="n"/>
       <c r="U69" s="3" t="n"/>
@@ -5822,11 +5810,7 @@
           <t>CLUB_S1973_74_0375</t>
         </is>
       </c>
-      <c r="R70" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
+      <c r="R70" s="3" t="n"/>
       <c r="S70" s="3" t="n"/>
       <c r="T70" s="3" t="n"/>
       <c r="U70" s="3" t="n"/>
@@ -17244,6 +17228,11 @@
           <t>CLUB_S1972_73_0441</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>TR_S1973_74_00374</t>
@@ -18602,6 +18591,11 @@
       <c r="R37" t="inlineStr">
         <is>
           <t>CLUB_S1972_73_0542</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -21409,7 +21403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21486,7 +21480,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1973_74_0064 'TJ Spartak Lada Soběslav' ROZBITÝ prev CLUB_S1972_73_0117 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -21498,7 +21492,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1973_74_0086 'TJ Žďas Žďár nad Sázavou' prev→CLUB_S1972_73_0455 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -21508,14 +21502,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1973_74_0013</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1973_74_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -21525,14 +21514,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1973_74_0025</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0025 'KVAL  skupina A' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21542,14 +21526,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1973_74_0026</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0026 'KVAL  skupina B' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21559,14 +21538,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1973_74_0027</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0027 'KVAL přímé postupy JM/SM' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -21576,17 +21550,372 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S1973_74_0028</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1973_74_0028 'KVAL skupina D (jen raw/prepared)' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1972_73_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1972_73_0537 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0139 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0094 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -30823,12 +31152,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -31038,12 +31367,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -31080,12 +31409,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -31705,12 +32034,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -32348,12 +32677,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -32484,12 +32813,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -32578,12 +32907,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -33174,12 +33503,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -33216,12 +33545,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0117</t>
+          <t>CLUB_S1972_73_0226</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Soběslav = TJ Spartak Lada Soběslav (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Tabor). **Lada Soběslav** = vyrobce auto-doplnku/dily. city Soběslav.</t>
+          <t>Soběslav = TJ Spartak Lada Soběslav (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Tabor). **Lada Soběslav** = vyrobce auto-doplnku/dily. city Soběslav. || TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -33352,12 +33681,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -33567,12 +33896,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -33824,12 +34153,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -34810,12 +35139,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Vyšné Opátske = TJ Pokrok Vyšné Opátske (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj (okres Sabinov). 'Opátske' bez diakritiky. NE Vysné Opátske mestska cast Kosic! city Vyšné Opátske.</t>
+          <t>Vyšné Opátske = TJ Pokrok Vyšné Opátske (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj (okres Sabinov). 'Opátske' bez diakritiky. NE Vysné Opátske mestska cast Kosic! city Vyšné Opátske. || TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Pokrok Vyšné Opátske</t>
+          <t>Vyšné Opátske</t>
         </is>
       </c>
     </row>
@@ -35146,12 +35475,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -35187,6 +35516,7 @@
         </is>
       </c>
     </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -35251,6 +35581,7 @@
         </is>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -35662,12 +35993,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Ruzyne = TJ Ruzyně EGU (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 6 (letiste). **EGU** = Energeticky vyzkumny ustav nebo Elektrotechnicky/Energo podnik. city Praha (Ruzyně).</t>
+          <t>Ruzyne = TJ Ruzyně EGU (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 6 (letiste). **EGU** = Energeticky vyzkumny ustav nebo Elektrotechnicky/Energo podnik. city Praha (Ruzyně). || TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Praha (Ruzyně)</t>
+          <t>Ruzyně EGU</t>
         </is>
       </c>
     </row>
@@ -37812,12 +38143,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -37943,12 +38274,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou.</t>
+          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou. || TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Týnec nad Sázavou</t>
+          <t>Týnec nad Labem</t>
         </is>
       </c>
     </row>
@@ -40304,12 +40635,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -41518,12 +41849,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -42928,12 +43259,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -46042,14 +46373,9 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -46178,14 +46504,9 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -46272,14 +46593,9 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -46319,14 +46635,9 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0018</t>
-        </is>
-      </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -47023,12 +47334,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -48229,12 +48540,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -50329,12 +50640,12 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -52141,12 +52452,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -52883,12 +53194,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -55923,11 +56234,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -55972,21 +56283,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0064</t>
+          <t>CLUB_S1973_74_0010</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0064 'TJ Spartak Lada Soběslav' ROZBITÝ prev CLUB_S1972_73_0117 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -55994,21 +56303,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0086</t>
+          <t>CLUB_S1973_74_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0086 'TJ Žďas Žďár nad Sázavou' prev→CLUB_S1972_73_0455 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -56016,21 +56323,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1973_74_0013</t>
+          <t>CLUB_S1973_74_0016</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1973_74_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1973_74_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -56038,21 +56343,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1973_74_0025</t>
+          <t>CLUB_S1973_74_0031</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1973_74_0025 'KVAL  skupina A' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -56060,21 +56363,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1973_74_0026</t>
+          <t>CLUB_S1973_74_0045</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1973_74_0026 'KVAL  skupina B' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -56082,21 +56383,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1973_74_0027</t>
+          <t>CLUB_S1973_74_0048</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1973_74_0027 'KVAL přímé postupy JM/SM' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -56104,24 +56403,622 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S1973_74_0028</t>
+          <t>CLUB_S1973_74_0050</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1973_74_0028 'KVAL skupina D (jen raw/prepared)' (L45, parent=NODE_S1973_74_0024) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0058</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0063</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0064</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0067</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0072</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0078</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0086</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1972_73_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0091</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1972_73_0537 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0101</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0109</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0129</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0130</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0139 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0180</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0183</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0237</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0264</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0277</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0294</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0369</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0372</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0374</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0375</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0392</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0420</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0454</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0466</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0474</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0094 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0489</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0507</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1973_74_0524</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -58953,7 +59850,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0117</t>
+          <t>CLUB_S1972_73_0226</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21403,7 +21403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21480,7 +21480,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -21492,7 +21492,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -21504,7 +21504,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -21516,7 +21516,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21528,7 +21528,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21540,7 +21540,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -21552,7 +21552,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1972_73_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21564,7 +21564,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1972_73_0537 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21576,7 +21576,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21588,7 +21588,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21600,7 +21600,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21612,7 +21612,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0139 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21624,7 +21624,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21636,7 +21636,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1972_73_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21648,7 +21648,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1972_73_0537 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21660,7 +21660,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21672,7 +21672,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21684,7 +21684,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21696,7 +21696,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0139 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21708,7 +21708,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21720,7 +21720,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -21732,7 +21732,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21744,7 +21744,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0094 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21756,166 +21756,10 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0094 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21932,7 +21776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21991,6 +21835,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22033,6 +21882,11 @@
           <t>12 týmů, jeden stůl. Mistr: Dukla Jihlava. Bez playoff.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22248,6 +22102,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22290,6 +22149,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22330,6 +22194,11 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0008</t>
         </is>
       </c>
     </row>
@@ -31152,12 +31021,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -31367,12 +31236,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -31409,12 +31278,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32034,12 +31903,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -32677,12 +32546,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -32813,12 +32682,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -34153,12 +34022,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -38274,12 +38143,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou. || TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Týnec nad Labem</t>
+          <t>Týnec nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -43259,12 +43128,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -47334,12 +47203,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -48540,12 +48409,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -52452,12 +52321,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -53194,12 +53063,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -56234,7 +56103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56288,12 +56157,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0010</t>
+          <t>CLUB_S1973_74_0050</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56308,12 +56177,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0015</t>
+          <t>CLUB_S1973_74_0058</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -56328,12 +56197,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0016</t>
+          <t>CLUB_S1973_74_0063</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56348,12 +56217,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0031</t>
+          <t>CLUB_S1973_74_0064</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -56368,12 +56237,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0045</t>
+          <t>CLUB_S1973_74_0067</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56388,12 +56257,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0048</t>
+          <t>CLUB_S1973_74_0072</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56408,12 +56277,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0050</t>
+          <t>CLUB_S1973_74_0086</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1972_73_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56428,12 +56297,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0058</t>
+          <t>CLUB_S1973_74_0091</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1972_73_0537 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56448,12 +56317,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0063</t>
+          <t>CLUB_S1973_74_0101</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56468,12 +56337,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0064</t>
+          <t>CLUB_S1973_74_0109</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1972_73_0226 'Spartak Soběslav'; ověřit [fix_broken_prev_d42]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56488,12 +56357,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0067</t>
+          <t>CLUB_S1973_74_0129</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56508,12 +56377,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0072</t>
+          <t>CLUB_S1973_74_0130</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0139 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56528,12 +56397,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0078</t>
+          <t>CLUB_S1973_74_0180</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56548,12 +56417,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0086</t>
+          <t>CLUB_S1973_74_0237</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1972_73_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56568,12 +56437,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0091</t>
+          <t>CLUB_S1973_74_0264</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1972_73_0537 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56588,12 +56457,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0101</t>
+          <t>CLUB_S1973_74_0277</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -56608,12 +56477,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0109</t>
+          <t>CLUB_S1973_74_0369</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56628,12 +56497,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0129</t>
+          <t>CLUB_S1973_74_0372</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56648,12 +56517,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0130</t>
+          <t>CLUB_S1973_74_0374</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0139 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56668,12 +56537,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0180</t>
+          <t>CLUB_S1973_74_0375</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56688,12 +56557,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0183</t>
+          <t>CLUB_S1973_74_0454</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -56708,12 +56577,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0237</t>
+          <t>CLUB_S1973_74_0466</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56728,12 +56597,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0264</t>
+          <t>CLUB_S1973_74_0474</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0094 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56748,277 +56617,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1973_74_0277</t>
+          <t>CLUB_S1973_74_0489</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0294</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0369</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0372</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0374</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0375</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0392</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0420</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0454</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0466</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0474</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1972_73_0094 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0489</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0507</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1973_74_0524</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F38"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -28815,7 +28815,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M5" t="n">
         <v>54</v>
@@ -29705,7 +29705,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M17" t="n">
         <v>63</v>
@@ -29853,7 +29853,7 @@
         <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M20" t="n">
         <v>56</v>
@@ -30165,7 +30165,7 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M26" t="n">
         <v>30</v>
@@ -30487,7 +30487,7 @@
         <v>36</v>
       </c>
       <c r="J27" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -61538,13 +61538,13 @@
         <v>20</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J36" t="n">
         <v>94</v>
@@ -61558,7 +61558,7 @@
         <v>91</v>
       </c>
       <c r="M36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -63047,7 +63047,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M57" t="n">
         <v>8</v>

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -35385,7 +35385,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -35450,7 +35449,6 @@
         </is>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -21776,7 +21776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L120"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21838,6 +21838,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -22102,6 +22102,16 @@
           <t>NODE_S1973_74_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22116,6 +22126,14 @@
         <is>
           <t>NODE_S1972_73_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -22149,6 +22167,8 @@
           <t>NODE_S1973_74_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22163,6 +22183,14 @@
         <is>
           <t>NODE_S1972_73_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -22196,6 +22224,8 @@
           <t>NODE_S1973_74_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22210,6 +22240,14 @@
         <is>
           <t>NODE_S1972_73_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -23333,6 +23371,8 @@
           <t>NODE_S1973_74_0029</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23342,6 +23382,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -23459,6 +23507,8 @@
           <t>NODE_S1973_74_0031</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23468,6 +23518,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -24519,6 +24577,8 @@
           <t>NODE_S1973_74_0058</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24528,6 +24588,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -25416,6 +25484,8 @@
           <t>NODE_S1973_74_0078</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25425,6 +25495,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -25836,6 +25914,8 @@
           <t>NODE_S1973_74_0088</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25845,6 +25925,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -26602,6 +26690,8 @@
           <t>NODE_S1973_74_0100</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26611,6 +26701,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -26770,6 +26868,8 @@
           <t>NODE_S1973_74_0100</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26779,6 +26879,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="117">

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -720,6 +720,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -22167,8 +22172,6 @@
           <t>NODE_S1973_74_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22224,8 +22227,6 @@
           <t>NODE_S1973_74_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23371,8 +23372,6 @@
           <t>NODE_S1973_74_0029</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23507,8 +23506,6 @@
           <t>NODE_S1973_74_0031</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24577,8 +24574,6 @@
           <t>NODE_S1973_74_0058</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25484,8 +25479,6 @@
           <t>NODE_S1973_74_0078</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25914,8 +25907,6 @@
           <t>NODE_S1973_74_0088</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26690,8 +26681,6 @@
           <t>NODE_S1973_74_0100</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26868,8 +26857,6 @@
           <t>NODE_S1973_74_0100</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -55937,7 +55924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56205,6 +56192,18 @@
       <c r="B23" t="inlineStr">
         <is>
           <t>Slovenská divize východ: utkání Detva – Vyšné Opátske 14:6 je v PDF označeno jako zdrojová záhada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1973_74_FINAL.xlsx
+++ b/data/S1973_74_FINAL.xlsx
@@ -35490,6 +35490,7 @@
         </is>
       </c>
     </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -35554,6 +35555,7 @@
         </is>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
